--- a/v5/AnalysisSummary_407409.xlsx
+++ b/v5/AnalysisSummary_407409.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c s="6" t="inlineStr" r="D24">
         <is>
-          <t xml:space="preserve">09-Jun-2026 10:28 ET</t>
+          <t xml:space="preserve">09-Jun-2026 12:05 ET</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c s="4" t="inlineStr" r="B41">
         <is>
-          <t xml:space="preserve">Intangible Asset / Total Asset: PWAVG Min 0 %</t>
+          <t xml:space="preserve">A Losses * : PWAVG Min 0 %</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="C41">
@@ -1118,10 +1118,10 @@
         <v>30</v>
       </c>
       <c s="20" r="E41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c s="20" r="F41">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="0">
@@ -1130,7 +1130,7 @@
       </c>
       <c s="4" t="inlineStr" r="B42">
         <is>
-          <t xml:space="preserve">Intangible Asset / Total Revenue: PWAVG Min 0 %</t>
+          <t xml:space="preserve">Inventories / Revenue: PWAVG Min 0 % &amp; Max 25 %</t>
         </is>
       </c>
       <c s="19" t="inlineStr" r="C42">
@@ -1139,232 +1139,136 @@
         </is>
       </c>
       <c s="20" r="D42">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c s="20" r="E42">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c s="20" r="F42">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="0">
-      <c s="5" r="A43">
-        <v>9</v>
-      </c>
-      <c s="4" t="inlineStr" r="B43">
-        <is>
-          <t xml:space="preserve">Inventories / Revenue: PWAVG Min 0 % &amp; Max 25 %</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="C43">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="20" r="D43">
-        <v>29</v>
-      </c>
-      <c s="20" r="E43">
-        <v>8</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="0">
+      <c s="15" t="inlineStr" r="A43">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="B43">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="C43">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="D43">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="15" t="inlineStr" r="E43">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
       </c>
       <c s="20" r="F43">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="0">
-      <c s="5" r="A44">
-        <v>10</v>
-      </c>
-      <c s="4" t="inlineStr" r="B44">
-        <is>
-          <t xml:space="preserve">Losses * : PWAVG Min 0 %</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="C44">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="20" r="D44">
-        <v>30</v>
-      </c>
-      <c s="20" r="E44">
-        <v>1</v>
-      </c>
-      <c s="20" r="F44">
         <v>21</v>
       </c>
     </row>
+    <row r="44" ht="14.3" customHeight="1"/>
     <row r="45" ht="18" customHeight="0">
-      <c s="5" r="A45">
-        <v>11</v>
-      </c>
-      <c s="4" t="inlineStr" r="B45">
-        <is>
-          <t xml:space="preserve">Net PPE / Revenue: PWAVG Min 0 %</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="C45">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="20" r="D45">
-        <v>29</v>
-      </c>
-      <c s="20" r="E45">
-        <v>0</v>
-      </c>
-      <c s="20" r="F45">
-        <v>21</v>
+      <c s="8" t="inlineStr" r="A45">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c s="18" t="inlineStr" r="B45">
+        <is>
+          <t xml:space="preserve">Qualitative Screening</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="C45">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="D45">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="E45">
+        <is>
+          <t xml:space="preserve">Excluded</t>
+        </is>
+      </c>
+      <c s="9" t="inlineStr" r="F45">
+        <is>
+          <t xml:space="preserve">Remaining</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="18" customHeight="0">
       <c s="5" r="A46">
+        <v>9</v>
+      </c>
+      <c s="4" t="inlineStr" r="B46">
+        <is>
+          <t xml:space="preserve">Business Description</t>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="C46">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="19" t="inlineStr" r="D46">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="20" r="E46">
         <v>12</v>
       </c>
-      <c s="4" t="inlineStr" r="B46">
-        <is>
-          <t xml:space="preserve">R&amp;D Expense / Revenue: PWAVG Min 0 %</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="C46">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="20" r="D46">
-        <v>3</v>
-      </c>
-      <c s="20" r="E46">
-        <v>0</v>
-      </c>
-      <c s="20" r="F46">
-        <v>21</v>
+      <c s="21" r="F46">
+        <v>9</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="0">
-      <c s="15" t="inlineStr" r="A47">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="15" t="inlineStr" r="B47">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="15" t="inlineStr" r="C47">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="15" t="inlineStr" r="D47">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="15" t="inlineStr" r="E47">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="20" r="F47">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" ht="14.3" customHeight="1"/>
-    <row r="49" ht="18" customHeight="0">
-      <c s="8" t="inlineStr" r="A49">
-        <is>
-          <t xml:space="preserve">#</t>
-        </is>
-      </c>
-      <c s="18" t="inlineStr" r="B49">
-        <is>
-          <t xml:space="preserve">Qualitative Screening</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="C49">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="D49">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="E49">
-        <is>
-          <t xml:space="preserve">Excluded</t>
-        </is>
-      </c>
-      <c s="9" t="inlineStr" r="F49">
-        <is>
-          <t xml:space="preserve">Remaining</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="0">
-      <c s="5" r="A50">
-        <v>13</v>
-      </c>
-      <c s="4" t="inlineStr" r="B50">
-        <is>
-          <t xml:space="preserve">Business Description</t>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="C50">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="19" t="inlineStr" r="D50">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="20" r="E50">
-        <v>12</v>
-      </c>
-      <c s="21" r="F50">
+      <c s="22" t="inlineStr" r="A47">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="22" t="inlineStr" r="B47">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="22" t="inlineStr" r="C47">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="22" t="inlineStr" r="D47">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="22" t="inlineStr" r="E47">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c s="23" r="F47">
         <v>9</v>
       </c>
     </row>
-    <row r="51" ht="15.75" customHeight="0">
-      <c s="22" t="inlineStr" r="A51">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="22" t="inlineStr" r="B51">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="22" t="inlineStr" r="C51">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="22" t="inlineStr" r="D51">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="22" t="inlineStr" r="E51">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c s="23" r="F51">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c s="24" t="inlineStr" r="A52">
+    <row r="48" ht="18" customHeight="1">
+      <c s="24" t="inlineStr" r="A48">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -1402,7 +1306,7 @@
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="A36:E36"/>
     <mergeCell ref="B37:E37"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A48:F48"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
